--- a/artfynd/A 41021-2023 artfynd.xlsx
+++ b/artfynd/A 41021-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41021-2023 artfynd.xlsx
+++ b/artfynd/A 41021-2023 artfynd.xlsx
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95802210</v>
+        <v>95802203</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674503.1473366842</v>
+        <v>674503</v>
       </c>
       <c r="R2" t="n">
-        <v>6616959.426413417</v>
+        <v>6616960</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +754,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95802203</v>
+        <v>95802210</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,33 +795,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674503.1473366842</v>
+        <v>674503</v>
       </c>
       <c r="R3" t="n">
-        <v>6616959.426413417</v>
+        <v>6616960</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -875,19 +855,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
